--- a/docs/StructureDefinition-TiuDocument89259.xlsx
+++ b/docs/StructureDefinition-TiuDocument89259.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-TiuDocument89259.xlsx
+++ b/docs/StructureDefinition-TiuDocument89259.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-TiuDocument89259.xlsx
+++ b/docs/StructureDefinition-TiuDocument89259.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-TiuDocument89259.xlsx
+++ b/docs/StructureDefinition-TiuDocument89259.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-TiuDocument89259.xlsx
+++ b/docs/StructureDefinition-TiuDocument89259.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
